--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -64,7 +64,7 @@
     <t>20099414</t>
   </si>
   <si>
-    <t>SOKLIN SOFT PRPL1.3</t>
+    <t>SO KLN S P.V 1.44 KG</t>
   </si>
   <si>
     <t>5</t>
@@ -214,7 +214,7 @@
     <t>20091870</t>
   </si>
   <si>
-    <t>SKLN LQ WHT&amp;BRGHT510</t>
+    <t>SKLN LQ WHT&amp;BRGHT500</t>
   </si>
   <si>
     <t>20114428</t>
@@ -301,19 +301,19 @@
     <t>20133333</t>
   </si>
   <si>
-    <t>GENTLE GEN A/KRGT700</t>
+    <t>GNTLE GEN A.K 700 ML</t>
   </si>
   <si>
     <t>20141371</t>
   </si>
   <si>
-    <t>GNTLE GEN CMLLIA 700</t>
+    <t>GENTLE GEN CM 700 ML</t>
   </si>
   <si>
     <t>20141372</t>
   </si>
   <si>
-    <t>GENTLE GEN LILAC 700</t>
+    <t>GENTLE GEN LI 700 ML</t>
   </si>
   <si>
     <t>20135245</t>
@@ -349,43 +349,43 @@
     <t>20113567</t>
   </si>
   <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>GNTLE GEN M.B 700 ML</t>
   </si>
   <si>
     <t>20115959</t>
   </si>
   <si>
-    <t>GENTLE GEN FR.PE 700</t>
+    <t>GENTLE GEN FP 700 ML</t>
   </si>
   <si>
     <t>20115958</t>
   </si>
   <si>
-    <t>GENTLE GEN PRS.G 700</t>
+    <t>GENTLE GEN PG 700 ML</t>
   </si>
   <si>
     <t>20073805</t>
   </si>
   <si>
-    <t>SOKLN MGNLA&amp;BRES1.3</t>
+    <t>SO KLN RD/MG 1.44 KG</t>
   </si>
   <si>
     <t>20041483</t>
   </si>
   <si>
-    <t>SO/KLN SOFT P/RS1.3</t>
+    <t>SO KLN S P/R 1.44 KG</t>
   </si>
   <si>
     <t>20140806</t>
   </si>
   <si>
-    <t>SKLN EDP FL.DELIS1.3</t>
+    <t>SO KLN D.LS 1.44 KG</t>
   </si>
   <si>
     <t>20140804</t>
   </si>
   <si>
-    <t>SKLN EDP FLR BLNC1.3</t>
+    <t>SO KLN BLNC 1.44 KG</t>
   </si>
   <si>
     <t>20091352</t>
@@ -475,7 +475,7 @@
     <t>20113809</t>
   </si>
   <si>
-    <t>OXYKLIN DTRG LIQ 700</t>
+    <t>OXYKLIN DTRG LIQ 670</t>
   </si>
   <si>
     <t>12</t>
@@ -574,7 +574,7 @@
     <t>20094735</t>
   </si>
   <si>
-    <t>DOWNY SUNRISE 950</t>
+    <t>DOWNY SUNRISE 950 ML</t>
   </si>
   <si>
     <t>14</t>
@@ -586,43 +586,43 @@
     <t>20094733</t>
   </si>
   <si>
-    <t>DOWNY MYSTIQUE 900</t>
+    <t>DOWNY MYSTQ 875 ML</t>
   </si>
   <si>
     <t>20140221</t>
   </si>
   <si>
-    <t>DOWNY PASSION 875ML</t>
+    <t>DOWNY PASSION 875 ML</t>
   </si>
   <si>
     <t>20141324</t>
   </si>
   <si>
-    <t>DOWNY SUNSHINE 500ML</t>
+    <t>DOWNY S.SHINE 500 ML</t>
   </si>
   <si>
     <t>20141323</t>
   </si>
   <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
+    <t>DOWNY M.NIGHT 500 ML</t>
   </si>
   <si>
     <t>20080360</t>
   </si>
   <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
+    <t>DOWNY MYSTQ 550 ML</t>
   </si>
   <si>
     <t>20080361</t>
   </si>
   <si>
-    <t>DOWNY PASSION 550ML</t>
+    <t>DOWNY PASSION 550 ML</t>
   </si>
   <si>
     <t>20074226</t>
   </si>
   <si>
-    <t>DOWNY SUN.FRSH 550</t>
+    <t>DOWNY S.FRSH 550 ML</t>
   </si>
   <si>
     <t>20139145</t>
@@ -715,7 +715,7 @@
     <t>20119238</t>
   </si>
   <si>
-    <t>TOTAL DET.PERFUME750</t>
+    <t>TOTAL DET.PERFUME650</t>
   </si>
   <si>
     <t>20131516</t>
@@ -1174,7 +1174,7 @@
     <t>20129722</t>
   </si>
   <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
+    <t>BUKRIM LIQ.JRK NP520</t>
   </si>
   <si>
     <t>20138518</t>
@@ -1201,37 +1201,37 @@
     <t>20034450</t>
   </si>
   <si>
-    <t>MAMA/L JERUK NPS 650</t>
+    <t>M/LMN JRK NPS 690 G</t>
   </si>
   <si>
     <t>10004067</t>
   </si>
   <si>
-    <t>MAMA/L PCH LEMON 650</t>
+    <t>M/LMN PCH LMN 690 G</t>
   </si>
   <si>
     <t>20099424</t>
   </si>
   <si>
-    <t>MAMA LIME CHARCO 650</t>
+    <t>M/LIME CHARCO 690 G</t>
   </si>
   <si>
     <t>20052031</t>
   </si>
   <si>
-    <t>MAMA LIME GRN TEA650</t>
+    <t>M/LIME GRN TEA 690 G</t>
   </si>
   <si>
     <t>10004068</t>
   </si>
   <si>
-    <t>MAMA LIME POUCH 650</t>
+    <t>M/LIME POUCH 690 G</t>
   </si>
   <si>
     <t>20134303</t>
   </si>
   <si>
-    <t>MAMA/L YUZU+J/NPS650</t>
+    <t>M/LMN RE YUZU 690 G</t>
   </si>
   <si>
     <t>20090067</t>
@@ -1342,7 +1342,7 @@
     <t>20142277</t>
   </si>
   <si>
-    <t>MAMA LM GRN BTL 690</t>
+    <t>M/LIME JRK BTL 690 G</t>
   </si>
   <si>
     <t>20135845</t>
@@ -3020,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>15</v>
@@ -3040,7 +3040,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>15</v>
@@ -3060,7 +3060,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -202,25 +202,25 @@
     <t>20093627</t>
   </si>
   <si>
-    <t>SKLN LQD SKR STRW510</t>
+    <t>SOKLN LI SKRA 510 ML</t>
   </si>
   <si>
     <t>20123818</t>
   </si>
   <si>
-    <t>SKLN LQD PROV LVD510</t>
+    <t>SOKLN LI LVDR 510 ML</t>
   </si>
   <si>
     <t>20091870</t>
   </si>
   <si>
-    <t>SKLN LQ WHT&amp;BRGHT500</t>
+    <t>SOKLN LI W&amp;B 510 ML</t>
   </si>
   <si>
     <t>20114428</t>
   </si>
   <si>
-    <t>SKLN LQD KOR CMLA510</t>
+    <t>SOKLN LI KRN 510 ML</t>
   </si>
   <si>
     <t>9</t>
@@ -319,31 +319,31 @@
     <t>20135245</t>
   </si>
   <si>
-    <t>SO KLIN LIQ FRNCH700</t>
+    <t>SOKLN DT FL 700 ML</t>
   </si>
   <si>
     <t>20133798</t>
   </si>
   <si>
-    <t>SO KLIN LIQ EN.RS700</t>
+    <t>SOKLN DT ER 700 ML</t>
   </si>
   <si>
     <t>20139729</t>
   </si>
   <si>
-    <t>SOKLN GR.TEA&amp;JSM 700</t>
+    <t>SOKLN DT GRN 700 ML</t>
   </si>
   <si>
     <t>20142134</t>
   </si>
   <si>
-    <t>SO KLN BLU PETAL 700</t>
+    <t>SOKLN DT BL P 700 ML</t>
   </si>
   <si>
     <t>20142132</t>
   </si>
   <si>
-    <t>SO KLN MAISON DE 700</t>
+    <t>SOKLN DT MDF 700 ML</t>
   </si>
   <si>
     <t>20113567</t>
@@ -661,7 +661,7 @@
     <t>20064413</t>
   </si>
   <si>
-    <t>ATCK JAZ1 S/CNTA 1.3</t>
+    <t>ATTACK JAZ CN 1.5 KG</t>
   </si>
   <si>
     <t>16</t>
@@ -670,19 +670,19 @@
     <t>20064414</t>
   </si>
   <si>
-    <t>ATTACK JAZ1 P/SGR1.3</t>
+    <t>ATTACK JAZ SG 1.5 KG</t>
   </si>
   <si>
     <t>20130527</t>
   </si>
   <si>
-    <t>ATTACK DET+SF RB 1.2</t>
+    <t>ATTACK JAZ RS 1.4 KG</t>
   </si>
   <si>
     <t>20138108</t>
   </si>
   <si>
-    <t>JAZ 1 PRPL BLS 1.2KG</t>
+    <t>ATTACK JAZ PR 1.4 KG</t>
   </si>
   <si>
     <t>20071827</t>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="649">
   <si>
     <t/>
   </si>
@@ -238,921 +238,915 @@
     <t>RINSO P.BRZE BTL 650</t>
   </si>
   <si>
-    <t>20131730</t>
-  </si>
-  <si>
-    <t>SYANG LIQ R/ROSE 700</t>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20143785</t>
+  </si>
+  <si>
+    <t>IDM D/C AUTUM SNT700</t>
+  </si>
+  <si>
+    <t>20139955</t>
+  </si>
+  <si>
+    <t>BU KRM JNHAE CB700ML</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GNTLE GEN A.K 700 ML</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GENTLE GEN CM 700 ML</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LI 700 ML</t>
+  </si>
+  <si>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SOKLN DT FL 700 ML</t>
+  </si>
+  <si>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SOKLN DT ER 700 ML</t>
+  </si>
+  <si>
+    <t>20139729</t>
+  </si>
+  <si>
+    <t>SOKLN DT GRN 700 ML</t>
+  </si>
+  <si>
+    <t>20142134</t>
+  </si>
+  <si>
+    <t>SOKLN DT BL P 700 ML</t>
+  </si>
+  <si>
+    <t>20142132</t>
+  </si>
+  <si>
+    <t>SOKLN DT MDF 700 ML</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GNTLE GEN M.B 700 ML</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FP 700 ML</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PG 700 ML</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SO KLN RD/MG 1.44 KG</t>
+  </si>
+  <si>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO KLN S P/R 1.44 KG</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN D.LS 1.44 KG</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN BLNC 1.44 KG</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA PWDR VLT PSN1.4</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK1.4</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PWDR PUTIH1.4KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HJB CLN&amp;FRSH1.4</t>
+  </si>
+  <si>
+    <t>20142276</t>
+  </si>
+  <si>
+    <t>DAIA PWDR LLY&amp;JSM1.4</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA PWDR FLORAL1.4</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA PWDR PUTIH 725G</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 725G</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SKLN SFTG LVD&amp;LLY650</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 650G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 650</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA PWDR VLT PSN725</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK725</t>
+  </si>
+  <si>
+    <t>20113809</t>
+  </si>
+  <si>
+    <t>OXYKLIN DTRG LIQ 670</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>20097739</t>
+  </si>
+  <si>
+    <t>IDM DET.CAIR PCH 700</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20067586</t>
+  </si>
+  <si>
+    <t>SOKLIN LIQ.BM TOP700</t>
+  </si>
+  <si>
+    <t>20054610</t>
+  </si>
+  <si>
+    <t>RINSO LIQ FRONT 1.45</t>
+  </si>
+  <si>
+    <t>10030924</t>
+  </si>
+  <si>
+    <t>SOKLIN MTC F/LD 900G</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V600</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 600</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950 ML</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTQ 875 ML</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 875 ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY S.SHINE 500 ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY M.NIGHT 500 ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTQ 550 ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550 ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY S.FRSH 550 ML</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ CN 1.5 KG</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ SG 1.5 KG</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ RS 1.4 KG</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ PR 1.4 KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL650</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME650</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 375G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK390</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20141985</t>
+  </si>
+  <si>
+    <t>SO KLN TROP SUMR 780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20142219</t>
+  </si>
+  <si>
+    <t>MLTO GNTL FRSH 765ML</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KRBL CMR 720 G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 720G</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH720G</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>10010480</t>
+  </si>
+  <si>
+    <t>SPR PELL FRS.APEL760</t>
+  </si>
+  <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>20137408</t>
+  </si>
+  <si>
+    <t>SPR PELL SAKURA 760</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF760</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE760</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 760</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 760</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20141956</t>
+  </si>
+  <si>
+    <t>EKONOMI NANAS 920G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20143785</t>
-  </si>
-  <si>
-    <t>IDM D/C AUTUM SNT700</t>
-  </si>
-  <si>
-    <t>20139955</t>
-  </si>
-  <si>
-    <t>BU KRM JNHAE CB700ML</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GNTLE GEN A.K 700 ML</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GENTLE GEN CM 700 ML</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LI 700 ML</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SOKLN DT FL 700 ML</t>
-  </si>
-  <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SOKLN DT ER 700 ML</t>
-  </si>
-  <si>
-    <t>20139729</t>
-  </si>
-  <si>
-    <t>SOKLN DT GRN 700 ML</t>
-  </si>
-  <si>
-    <t>20142134</t>
-  </si>
-  <si>
-    <t>SOKLN DT BL P 700 ML</t>
-  </si>
-  <si>
-    <t>20142132</t>
-  </si>
-  <si>
-    <t>SOKLN DT MDF 700 ML</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GNTLE GEN M.B 700 ML</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FP 700 ML</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PG 700 ML</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SO KLN RD/MG 1.44 KG</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO KLN S P/R 1.44 KG</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN D.LS 1.44 KG</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN BLNC 1.44 KG</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA PWDR VLT PSN1.4</t>
-  </si>
-  <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK1.4</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PWDR PUTIH1.4KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HJB CLN&amp;FRSH1.4</t>
-  </si>
-  <si>
-    <t>20142276</t>
-  </si>
-  <si>
-    <t>DAIA PWDR LLY&amp;JSM1.4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA PWDR FLORAL1.4</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA PWDR PUTIH 725G</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 725G</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SKLN SFTG LVD&amp;LLY650</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 650G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 650</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA PWDR VLT PSN725</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK725</t>
-  </si>
-  <si>
-    <t>20113809</t>
-  </si>
-  <si>
-    <t>OXYKLIN DTRG LIQ 670</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>20097739</t>
-  </si>
-  <si>
-    <t>IDM DET.CAIR PCH 700</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20067586</t>
-  </si>
-  <si>
-    <t>SOKLIN LIQ.BM TOP700</t>
-  </si>
-  <si>
-    <t>20054610</t>
-  </si>
-  <si>
-    <t>RINSO LIQ FRONT 1.45</t>
-  </si>
-  <si>
-    <t>10030924</t>
-  </si>
-  <si>
-    <t>SOKLIN MTC F/LD 900G</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V600</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20142010</t>
-  </si>
-  <si>
-    <t>ROYALE MTCHA BLS 600</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950 ML</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTQ 875 ML</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 875 ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY S.SHINE 500 ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY M.NIGHT 500 ML</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTQ 550 ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550 ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY S.FRSH 550 ML</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ CN 1.5 KG</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ SG 1.5 KG</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ RS 1.4 KG</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ PR 1.4 KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL650</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME650</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 375G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK390</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20141985</t>
-  </si>
-  <si>
-    <t>SO KLN TROP SUMR 780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20142219</t>
-  </si>
-  <si>
-    <t>MLTO GNTL FRSH 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 720G</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH720G</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>10010480</t>
-  </si>
-  <si>
-    <t>SPR PELL FRS.APEL760</t>
-  </si>
-  <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
-    <t>20137408</t>
-  </si>
-  <si>
-    <t>SPR PELL SAKURA 760</t>
-  </si>
-  <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>20089486</t>
-  </si>
-  <si>
-    <t>IDM KRBL SRH CTR 650</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF760</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE760</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 760</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 760</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20141956</t>
-  </si>
-  <si>
-    <t>EKONOMI NANAS 920G</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
     <t>20092331</t>
   </si>
   <si>
@@ -1252,7 +1246,7 @@
     <t>20112492</t>
   </si>
   <si>
-    <t>SUNLIGHT JRK NPS400G</t>
+    <t>SNLGHT JRK NPS 400 G</t>
   </si>
   <si>
     <t>20143097</t>
@@ -1864,7 +1858,7 @@
     <t>10005198</t>
   </si>
   <si>
-    <t>HIT INS.SPRAY ORG600</t>
+    <t>HIT IS ORG KG 600+50</t>
   </si>
   <si>
     <t>20109613</t>
@@ -1957,7 +1951,7 @@
     <t>10006651</t>
   </si>
   <si>
-    <t>VAPE FMK ORANGE 600</t>
+    <t>VAPE FMK ORN 600 ML</t>
   </si>
   <si>
     <t>20142133</t>
@@ -2356,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F299"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3000,18 +2994,18 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -3020,7 +3014,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>15</v>
@@ -3028,10 +3022,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3040,27 +3034,27 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -3068,10 +3062,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -3080,7 +3074,7 @@
         <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -3088,10 +3082,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -3100,7 +3094,7 @@
         <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3108,10 +3102,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -3120,7 +3114,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -3128,10 +3122,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3140,10 +3134,10 @@
         <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3160,18 +3154,18 @@
         <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3180,7 +3174,7 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -3188,10 +3182,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3200,7 +3194,7 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3208,19 +3202,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3228,10 +3222,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -3240,7 +3234,7 @@
         <v>35</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3248,10 +3242,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3260,18 +3254,18 @@
         <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -3280,18 +3274,18 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3300,7 +3294,7 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -3308,10 +3302,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3320,7 +3314,7 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3328,10 +3322,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3340,7 +3334,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3348,10 +3342,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3360,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3368,19 +3362,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3388,10 +3382,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3400,7 +3394,7 @@
         <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3408,10 +3402,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3420,18 +3414,18 @@
         <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3440,38 +3434,38 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3480,7 +3474,7 @@
         <v>70</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3488,10 +3482,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3500,7 +3494,7 @@
         <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3508,10 +3502,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3520,7 +3514,7 @@
         <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3528,19 +3522,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3557,50 +3551,50 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3608,19 +3602,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3637,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3648,19 +3642,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3668,19 +3662,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3688,19 +3682,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3708,19 +3702,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3737,33 +3731,33 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3777,73 +3771,73 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,10 +3851,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3868,19 +3862,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3888,19 +3882,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3908,19 +3902,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3928,19 +3922,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3948,19 +3942,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3968,19 +3962,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3988,79 +3982,79 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>15</v>
@@ -4068,19 +4062,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>15</v>
@@ -4088,19 +4082,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4108,102 +4102,102 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4217,10 +4211,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>21</v>
@@ -4228,19 +4222,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -4248,19 +4242,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4268,22 +4262,22 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,73 +4291,73 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4377,10 +4371,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>21</v>
@@ -4388,19 +4382,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -4408,62 +4402,62 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4477,30 +4471,30 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>21</v>
@@ -4508,39 +4502,39 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4548,79 +4542,79 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4628,19 +4622,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4648,122 +4642,122 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,10 +4771,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4788,19 +4782,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4808,19 +4802,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4828,19 +4822,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4848,19 +4842,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4868,19 +4862,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4888,19 +4882,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4908,22 +4902,22 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4937,10 +4931,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>21</v>
@@ -4948,42 +4942,42 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4997,50 +4991,50 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>21</v>
@@ -5048,19 +5042,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -5068,42 +5062,42 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5117,10 +5111,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -5128,22 +5122,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5157,113 +5151,113 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5277,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>21</v>
@@ -5288,19 +5282,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5308,19 +5302,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5328,39 +5322,39 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -5368,99 +5362,99 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>94</v>
+        <v>338</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>21</v>
@@ -5468,122 +5462,122 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5597,70 +5591,70 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5668,19 +5662,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5688,19 +5682,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5708,19 +5702,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5728,19 +5722,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5757,13 +5751,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5777,13 +5771,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5797,10 +5791,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5817,10 +5811,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5837,10 +5831,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5857,13 +5851,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,30 +5871,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5917,10 +5911,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5937,10 +5931,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5957,10 +5951,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5977,10 +5971,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5997,10 +5991,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6017,13 +6011,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>377</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6037,33 +6031,33 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>21</v>
+        <v>246</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6077,13 +6071,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6097,13 +6091,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6117,13 +6111,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6137,13 +6131,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6157,13 +6151,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6177,13 +6171,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6197,30 +6191,30 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>21</v>
@@ -6237,10 +6231,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6257,13 +6251,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6277,13 +6271,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6297,10 +6291,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>21</v>
@@ -6308,19 +6302,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6337,10 +6331,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6357,13 +6351,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6377,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>377</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,13 +6391,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,13 +6411,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,13 +6431,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>341</v>
+        <v>91</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,30 +6471,30 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>21</v>
@@ -6517,10 +6511,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6537,13 +6531,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,13 +6551,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,13 +6571,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6597,13 +6591,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>157</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,33 +6611,33 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>160</v>
+        <v>469</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>471</v>
+        <v>309</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6657,13 +6651,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>312</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6677,33 +6671,33 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>471</v>
+        <v>377</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E217" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6717,13 +6711,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6737,13 +6731,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6751,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6777,13 +6771,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6797,13 +6791,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>294</v>
+        <v>377</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6817,13 +6811,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>77</v>
+        <v>377</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6837,13 +6831,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>77</v>
+        <v>377</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6857,13 +6851,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6877,10 +6871,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>5</v>
@@ -6897,10 +6891,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -6917,13 +6911,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>5</v>
+        <v>291</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6937,13 +6931,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6957,13 +6951,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6977,13 +6971,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>294</v>
+        <v>377</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6997,13 +6991,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>77</v>
+        <v>377</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,33 +7011,33 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>77</v>
+        <v>338</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7057,13 +7051,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,13 +7071,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7097,13 +7091,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,13 +7111,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,13 +7131,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,13 +7151,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,13 +7171,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7197,13 +7191,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,13 +7211,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7237,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7257,30 +7251,30 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7297,13 +7291,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7317,13 +7311,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7337,13 +7331,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7357,13 +7351,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7377,13 +7371,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7397,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,13 +7411,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7437,13 +7431,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,13 +7451,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,13 +7471,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,13 +7491,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>312</v>
+        <v>377</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,13 +7511,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,13 +7531,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>94</v>
+        <v>309</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,13 +7551,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>312</v>
+        <v>91</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7577,33 +7571,33 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7617,13 +7611,13 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7637,13 +7631,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,13 +7651,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7697,10 +7691,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>5</v>
@@ -7717,10 +7711,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>5</v>
@@ -7737,13 +7731,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,13 +7751,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7777,13 +7771,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7797,13 +7791,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>294</v>
+        <v>377</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7817,13 +7811,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>77</v>
+        <v>377</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -7837,33 +7831,33 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="E275" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7877,13 +7871,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7897,13 +7891,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7917,33 +7911,33 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>312</v>
+        <v>605</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>607</v>
+        <v>309</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7957,13 +7951,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7977,13 +7971,13 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7997,13 +7991,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8017,13 +8011,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8037,13 +8031,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8057,10 +8051,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>5</v>
@@ -8077,13 +8071,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8097,33 +8091,33 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="E288" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8137,13 +8131,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8157,13 +8151,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8177,13 +8171,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8197,13 +8191,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8217,13 +8211,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8237,13 +8231,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,10 +8251,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>5</v>
@@ -8277,10 +8271,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -8297,10 +8291,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8317,13 +8311,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8337,32 +8331,12 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="E300" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F300" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="652">
   <si>
     <t/>
   </si>
@@ -100,13 +100,13 @@
     <t>20067585</t>
   </si>
   <si>
-    <t>SKLN LQD SC/BLOSM700</t>
+    <t>SKLN LIQ SCR/BLSM675</t>
   </si>
   <si>
     <t>20054747</t>
   </si>
   <si>
-    <t>SKLIN LQD V/BLSOM700</t>
+    <t>SKLN LIQ VLT BLSM675</t>
   </si>
   <si>
     <t>6</t>
@@ -115,7 +115,7 @@
     <t>20046548</t>
   </si>
   <si>
-    <t>SKLIN LQD SFTRGN 700</t>
+    <t>SKLIN LIQ SFTRGN 675</t>
   </si>
   <si>
     <t>7</t>
@@ -124,7 +124,7 @@
     <t>20137791</t>
   </si>
   <si>
-    <t>SO KLIN LIQ HJB 700</t>
+    <t>SKLN LIQ HJB COOL675</t>
   </si>
   <si>
     <t>8</t>
@@ -202,25 +202,25 @@
     <t>20093627</t>
   </si>
   <si>
-    <t>SOKLN LI SKRA 510 ML</t>
+    <t>SKLN LIQ SKRA STR500</t>
   </si>
   <si>
     <t>20123818</t>
   </si>
   <si>
-    <t>SOKLN LI LVDR 510 ML</t>
+    <t>SKLN LIQ PRV LVDR500</t>
   </si>
   <si>
     <t>20091870</t>
   </si>
   <si>
-    <t>SOKLN LI W&amp;B 510 ML</t>
+    <t>SKLN LIQ C/A W&amp;B500</t>
   </si>
   <si>
     <t>20114428</t>
   </si>
   <si>
-    <t>SOKLN LI KRN 510 ML</t>
+    <t>SKLN LIQ KRN CMLA500</t>
   </si>
   <si>
     <t>9</t>
@@ -382,31 +382,31 @@
     <t>20091352</t>
   </si>
   <si>
-    <t>DAIA PWDR VLT PSN1.4</t>
+    <t>DAIA +SFT VLT 1.5 KG</t>
   </si>
   <si>
     <t>20052321</t>
   </si>
   <si>
-    <t>DAIA PWDR ROM/PNK1.4</t>
+    <t>DAIA SFT PINK 1.5 KG</t>
   </si>
   <si>
     <t>20030446</t>
   </si>
   <si>
-    <t>DAIA PWDR PUTIH1.4KG</t>
+    <t>DAIA PUTIH 1.5 KG</t>
   </si>
   <si>
     <t>20121050</t>
   </si>
   <si>
-    <t>DAIA HJB CLN&amp;FRSH1.4</t>
+    <t>DAIA HIJAB CF 1.5 KG</t>
   </si>
   <si>
     <t>20142276</t>
   </si>
   <si>
-    <t>DAIA PWDR LLY&amp;JSM1.4</t>
+    <t>DAIA LLY JSMN 1.5 KG</t>
   </si>
   <si>
     <t>10</t>
@@ -415,7 +415,7 @@
     <t>10014547</t>
   </si>
   <si>
-    <t>DAIA PWDR FLORAL1.4</t>
+    <t>DAIA B/FLWRL 1.5 KG</t>
   </si>
   <si>
     <t>20012007</t>
@@ -820,43 +820,43 @@
     <t>10005803</t>
   </si>
   <si>
-    <t>SOKLIN PWNGI RED 780</t>
+    <t>SOKLN PWG RED 780 ML</t>
   </si>
   <si>
     <t>10007389</t>
   </si>
   <si>
-    <t>SOKLIN PWNGI PINK780</t>
+    <t>SOKLN PWG PNK 780 ML</t>
   </si>
   <si>
     <t>10008104</t>
   </si>
   <si>
-    <t>SO KLIN PWG BLUE 780</t>
+    <t>SOKLN PWG BLU 780 ML</t>
   </si>
   <si>
     <t>20108418</t>
   </si>
   <si>
-    <t>SOKLIN PWG HJB GR780</t>
+    <t>SOKLN P HJB/G 780 ML</t>
   </si>
   <si>
     <t>10005802</t>
   </si>
   <si>
-    <t>SOKLIN PEWANGI VL780</t>
+    <t>SOKLN PWG VL 780 ML</t>
   </si>
   <si>
     <t>20141985</t>
   </si>
   <si>
-    <t>SO KLN TROP SUMR 780</t>
+    <t>SOKLN TRO SUM 780 ML</t>
   </si>
   <si>
     <t>20134526</t>
   </si>
   <si>
-    <t>SOKLIN PWG COT.FN780</t>
+    <t>SOKLN PWG C.F 780 ML</t>
   </si>
   <si>
     <t>20129370</t>
@@ -1036,18 +1036,18 @@
     <t>SOS P/LT APLL REF700</t>
   </si>
   <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
     <t>10010480</t>
   </si>
   <si>
     <t>SPR PELL FRS.APEL760</t>
   </si>
   <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
     <t>20137408</t>
   </si>
   <si>
@@ -1132,7 +1132,7 @@
     <t>20141956</t>
   </si>
   <si>
-    <t>EKONOMI NANAS 920G</t>
+    <t>EKNM NNAS JRK NPS910</t>
   </si>
   <si>
     <t>26</t>
@@ -1141,7 +1141,7 @@
     <t>20136124</t>
   </si>
   <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
+    <t>EKNM LIQ N&amp;JN 675 G</t>
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
@@ -1150,19 +1150,19 @@
     <t>20092331</t>
   </si>
   <si>
-    <t>EKONOMI LIQ JR.NP675</t>
+    <t>EKNM LIQ JR.N 650 ML</t>
   </si>
   <si>
     <t>20123812</t>
   </si>
   <si>
-    <t>EKONOMI LQ.SEREH 675</t>
+    <t>EKNM LQ.SREH 650 ML</t>
   </si>
   <si>
     <t>20107240</t>
   </si>
   <si>
-    <t>EKONOMI LIQ.SW&amp;JR675</t>
+    <t>EKNM LIQ.SW&amp;J 650 ML</t>
   </si>
   <si>
     <t>20129722</t>
@@ -1342,7 +1342,7 @@
     <t>20135845</t>
   </si>
   <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
+    <t>EKNM LIQ J&amp;LMN 650ML</t>
   </si>
   <si>
     <t>10029632</t>
@@ -1879,15 +1879,21 @@
     <t>HIT SPRY JPN.SKR 600</t>
   </si>
   <si>
+    <t>20144288</t>
+  </si>
+  <si>
+    <t>BYGN ORG BRZE 675ML</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>10003272</t>
   </si>
   <si>
     <t>BAYGON SPR CT 675 ML</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>20139446</t>
   </si>
   <si>
@@ -1900,64 +1906,67 @@
     <t>BAYGON FLO.GRDN 400</t>
   </si>
   <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORN 600 ML</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
     <t>20135247</t>
   </si>
   <si>
     <t>BAYGON FLRL.FNTSY500</t>
   </si>
   <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>20135248</t>
   </si>
   <si>
     <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORN 600 ML</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
   </si>
 </sst>
 </file>
@@ -2350,13 +2359,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F299"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2994,7 +3004,7 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>15</v>
@@ -3014,7 +3024,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>15</v>
@@ -3034,7 +3044,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -8097,7 +8107,7 @@
         <v>4</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>309</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8114,10 +8124,10 @@
         <v>624</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8134,10 +8144,10 @@
         <v>624</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8154,7 +8164,7 @@
         <v>624</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>309</v>
@@ -8174,7 +8184,7 @@
         <v>624</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>309</v>
@@ -8194,7 +8204,7 @@
         <v>624</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>309</v>
@@ -8214,10 +8224,10 @@
         <v>624</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>309</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8234,7 +8244,7 @@
         <v>624</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>5</v>
@@ -8254,7 +8264,7 @@
         <v>624</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>5</v>
@@ -8274,7 +8284,7 @@
         <v>624</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -8294,10 +8304,10 @@
         <v>624</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8314,10 +8324,10 @@
         <v>624</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8331,13 +8341,33 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
